--- a/data/processed/week_landing_audit.xlsx
+++ b/data/processed/week_landing_audit.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FBА79266</t>
+          <t>FBА79381</t>
         </is>
       </c>
     </row>
@@ -683,18 +683,6 @@
         </is>
       </c>
       <c r="B7" t="inlineStr">
-        <is>
-          <t>FBА79381</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>weekly_sales_snapshot</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -818,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,16 +1032,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AM-W22 Duplicate</t>
+          <t>TC40S</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2963.559322033898</v>
+        <v>2753.39</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1062,16 +1050,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TC40S</t>
+          <t>TIC-04</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2753.39</v>
+        <v>2372.033898305085</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1080,16 +1068,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TIC-04</t>
+          <t>TM310</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2372.033898305085</v>
+        <v>1948.31</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1103,11 +1091,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI_13</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2287.28813559322</v>
+        <v>1885.593220338983</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1116,16 +1104,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AM-C47 Duplicate</t>
+          <t>GS-04</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2117.796610169491</v>
+        <v>1770.338983050847</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1134,16 +1122,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TM310</t>
+          <t>VC-03 HEPA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1948.31</v>
+        <v>1688.135593220339</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1152,16 +1140,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1885.593220338983</v>
+        <v>661.9048</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1170,72 +1158,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS-04</t>
+          <t>AM-C13</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1770.338983050847</v>
+        <v>422.8813559322034</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>VC-03 HEPA</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1688.135593220339</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ETC-08-BL</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>661.9048</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AM-C13</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>422.8813559322034</v>
-      </c>
-      <c r="D23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1393,17 +1327,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13550.8</v>
+        <v>12706.79661016949</v>
       </c>
       <c r="D7" t="n">
-        <v>2769.5</v>
+        <v>2414.41</v>
       </c>
       <c r="E7" t="n">
-        <v>-79.59999999999999</v>
+        <v>-81</v>
       </c>
     </row>
     <row r="8">
@@ -1414,17 +1348,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10589</v>
+        <v>13550.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2414.41</v>
+        <v>2769.5</v>
       </c>
       <c r="E8" t="n">
-        <v>-77.2</v>
+        <v>-79.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1568,7 +1502,7 @@
         <v>158350.8474576271</v>
       </c>
       <c r="D15" t="n">
-        <v>63972.88135593222</v>
+        <v>63972.88135593221</v>
       </c>
       <c r="E15" t="n">
         <v>-59.6</v>
@@ -3063,7 +2997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5120,22 +5054,18 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79286</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>B0CR5G3NRL</t>
-        </is>
-      </c>
+          <t>FBA79260</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AX4611</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -5143,12 +5073,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79289</t>
+          <t>FBA79286</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0CRDG22TQ</t>
+          <t>B0CR5G3NRL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5158,7 +5088,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ES5278</t>
+          <t>AX4611</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5166,12 +5096,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79302</t>
+          <t>FBA79289</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0CR5QRNQN</t>
+          <t>B0CRDG22TQ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5181,7 +5111,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AR60076</t>
+          <t>ES5278</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5189,22 +5119,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79375</t>
+          <t>FBA79302</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0D2P6KF4N</t>
+          <t>B0CR5QRNQN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ET-03-BL</t>
+          <t>AR60076</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5212,22 +5142,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79389</t>
+          <t>FBA79375</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0D3M13T6H</t>
+          <t>B0D2P6KF4N</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AWB-01</t>
+          <t>ET-03-BL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5235,22 +5165,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79407</t>
+          <t>FBA79389</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0CWR5S3R7</t>
+          <t>B0D3M13T6H</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AX5385</t>
+          <t>AWB-01</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5258,12 +5188,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79408</t>
+          <t>FBA79407</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0CYN8F826</t>
+          <t>B0CWR5S3R7</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5273,7 +5203,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AX5616</t>
+          <t>AX5385</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5281,12 +5211,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79419</t>
+          <t>FBA79408</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0CZSF6LVY</t>
+          <t>B0CYN8F826</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5296,7 +5226,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FS6062</t>
+          <t>AX5616</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -5304,22 +5234,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79433</t>
+          <t>FBA79419</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0DC3JRBW1</t>
+          <t>B0CZSF6LVY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>WM-SE08-WD</t>
+          <t>FS6062</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -5327,12 +5257,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79434</t>
+          <t>FBA79433</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0DC3SJMZ6</t>
+          <t>B0DC3JRBW1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5342,7 +5272,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WM-USE06-WB</t>
+          <t>WM-SE08-WD</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -5350,12 +5280,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79435</t>
+          <t>FBA79434</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0DC3NPKGF</t>
+          <t>B0DC3SJMZ6</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5365,7 +5295,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>WM-USE06-WW</t>
+          <t>WM-USE06-WB</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -5373,22 +5303,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79461</t>
+          <t>FBA79435</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DC3NPKGF</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>WM-USE06-WW</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -5396,12 +5326,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79572</t>
+          <t>FBA79461</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0DKJVWM8Q</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5411,7 +5341,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LE-07</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -5419,22 +5349,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79579</t>
+          <t>FBA79572</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0CQX4GVSB</t>
+          <t>B0DKJVWM8Q</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>LE-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -5442,12 +5372,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79582</t>
+          <t>FBA79579</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0CQX4GVSB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5457,7 +5387,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TD510+</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -5465,22 +5395,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79588</t>
+          <t>FBA79582</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0DHRQPGGM</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EA-01 Pro</t>
+          <t>TD510+</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -5488,12 +5418,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79592</t>
+          <t>FBA79588</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0DMSMKRD9</t>
+          <t>B0DHRQPGGM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5503,7 +5433,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>FM-01</t>
+          <t>EA-01 Pro</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -5511,12 +5441,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79593</t>
+          <t>FBA79592</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0DMSSLXST</t>
+          <t>B0DMSMKRD9</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5526,7 +5456,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FM-02</t>
+          <t>FM-01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -5534,12 +5464,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79594</t>
+          <t>FBA79593</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0DM6MG4ZH</t>
+          <t>B0DMSSLXST</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5549,7 +5479,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EM-01</t>
+          <t>FM-02</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -5557,12 +5487,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79597</t>
+          <t>FBA79594</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0DNJHKZ2G</t>
+          <t>B0DM6MG4ZH</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5572,7 +5502,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BM-01</t>
+          <t>EM-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -5580,22 +5510,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79608</t>
+          <t>FBA79597</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0DSG2BD4H</t>
+          <t>B0DNJHKZ2G</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>HA1ML</t>
+          <t>BM-01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5603,12 +5533,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79609</t>
+          <t>FBA79608</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0DSG5PX7M</t>
+          <t>B0DSG2BD4H</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5618,7 +5548,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HA2ML</t>
+          <t>HA1ML</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -5626,12 +5556,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79610</t>
+          <t>FBA79609</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0DSG4F8D9</t>
+          <t>B0DSG5PX7M</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5641,7 +5571,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GS1ML</t>
+          <t>HA2ML</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5649,12 +5579,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79611</t>
+          <t>FBA79610</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0DSG694P2</t>
+          <t>B0DSG4F8D9</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5664,7 +5594,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GS2ML</t>
+          <t>GS1ML</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5672,22 +5602,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79619</t>
+          <t>FBA79611</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DJ2Z41C1</t>
+          <t>B0DSG694P2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AR11640</t>
+          <t>GS2ML</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5695,22 +5625,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79661</t>
+          <t>FBA79619</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0DQ51R95T</t>
+          <t>B0DJ2Z41C1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>WM-MODL-BK</t>
+          <t>AR11640</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -5718,12 +5648,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79663</t>
+          <t>FBA79661</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0DQPFL835</t>
+          <t>B0DQ51R95T</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5733,7 +5663,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>WM-LODJ-CF</t>
+          <t>WM-MODL-BK</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -5741,12 +5671,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79664</t>
+          <t>FBA79663</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0DQPKMRN1</t>
+          <t>B0DQPFL835</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5756,7 +5686,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>WM-LODJ-BK</t>
+          <t>WM-LODJ-CF</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -5764,12 +5694,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79665</t>
+          <t>FBA79664</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0DQPGZWPF</t>
+          <t>B0DQPKMRN1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5779,7 +5709,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>WM-LODJ-WH</t>
+          <t>WM-LODJ-BK</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5787,12 +5717,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79666</t>
+          <t>FBA79665</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0DQPG9FSN</t>
+          <t>B0DQPGZWPF</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5802,7 +5732,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WM-LODJ-IN</t>
+          <t>WM-LODJ-WH</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -5810,12 +5740,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79669</t>
+          <t>FBA79666</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0DQPLMQQ7</t>
+          <t>B0DQPG9FSN</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5825,7 +5755,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>WM-LWS-CF</t>
+          <t>WM-LODJ-IN</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -5833,12 +5763,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79670</t>
+          <t>FBA79668</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DQPGLK2T</t>
+          <t>B0DQPLCZ3G</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5848,7 +5778,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>WM-LWS-GR</t>
+          <t>WM-LODN-BK</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -5856,22 +5786,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79674</t>
+          <t>FBA79669</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0DV8XH455</t>
+          <t>B0DQPLMQQ7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>BM-03</t>
+          <t>WM-LWS-CF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5879,22 +5809,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79684</t>
+          <t>FBA79670</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0DVC9Q219</t>
+          <t>B0DQPGLK2T</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AP-02</t>
+          <t>WM-LWS-GR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -5902,12 +5832,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79688</t>
+          <t>FBA79674</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0DV8TR64D</t>
+          <t>B0DV8XH455</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5917,7 +5847,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MM-01</t>
+          <t>BM-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -5925,12 +5855,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79698</t>
+          <t>FBA79684</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0DTK4FY1G</t>
+          <t>B0DVC9Q219</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5940,7 +5870,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SS-01</t>
+          <t>AP-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -5948,22 +5878,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79726</t>
+          <t>FBA79688</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0DT2S2Y7F</t>
+          <t>B0DV8TR64D</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AR11673</t>
+          <t>MM-01</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -5971,22 +5901,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79729</t>
+          <t>FBA79698</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0DT2Y9HRM</t>
+          <t>B0DTK4FY1G</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AR11677</t>
+          <t>SS-01</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5994,22 +5924,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79779</t>
+          <t>FBA79726</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0F5X2C11Z</t>
+          <t>B0DT2S2Y7F</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SW-01</t>
+          <t>AR11673</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -6017,22 +5947,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79814</t>
+          <t>FBA79729</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0GNM35G8X</t>
+          <t>B0DT2Y9HRM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AH-50 Ear Cushion</t>
+          <t>AR11677</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -6040,22 +5970,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79837</t>
+          <t>FBA79779</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0FJ8V2LZM</t>
+          <t>B0F5X2C11Z</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AI-06 + AM-C45</t>
+          <t>SW-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -6063,22 +5993,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79854</t>
+          <t>FBA79814</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FFJ6T8YY</t>
+          <t>B0GNM35G8X</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AR11688</t>
+          <t>AH-50 Ear Cushion</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -6086,12 +6016,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA79837</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0FJ8V2LZM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6101,7 +6031,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AI-06 + AM-C45</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -6109,22 +6039,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79914</t>
+          <t>FBA79854</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0FYNR2XCB</t>
+          <t>B0FFJ6T8YY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ST-01 ST-01 Bowl</t>
+          <t>AR11688</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6132,12 +6062,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79974</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0GD8JSPB1</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6147,7 +6077,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -6155,12 +6085,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79914</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0FYNR2XCB</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6170,7 +6100,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>ST-01 ST-01 Bowl</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -6178,22 +6108,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79974</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GD8JSPB1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -6201,22 +6131,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -6224,22 +6154,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA80006</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>A2-XLR</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -6247,12 +6177,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6262,7 +6192,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -6270,12 +6200,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA80006</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6285,7 +6215,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>A2-XLR</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -6293,12 +6223,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA80011</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0GTZND3ZN</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6308,7 +6238,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AM-Pro16</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -6316,12 +6246,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA80012</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0GTZJF142</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6331,7 +6261,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>AM-Pro24</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -6339,12 +6269,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA80013</t>
+          <t>FBA80011</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0GTZLGPFR</t>
+          <t>B0GTZND3ZN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6354,7 +6284,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>XM-16</t>
+          <t>AM-Pro16</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -6362,12 +6292,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA80014</t>
+          <t>FBA80012</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0GTZ9X8Q2</t>
+          <t>B0GTZJF142</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6377,7 +6307,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>XM-24</t>
+          <t>AM-Pro24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -6385,22 +6315,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA80054</t>
+          <t>FBA80013</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0GF72W1XQ</t>
+          <t>B0GTZLGPFR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MK7583</t>
+          <t>XM-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6408,12 +6338,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA80074</t>
+          <t>FBA80014</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0GTZ9X8Q2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6423,7 +6353,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>XM-24</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6431,22 +6361,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA80075</t>
+          <t>FBA80054</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0GXPGBQB1</t>
+          <t>B0GF72W1XQ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+          <t>MK7583</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6454,12 +6384,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA80076</t>
+          <t>FBA80074</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6469,7 +6399,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6477,12 +6407,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA80077</t>
+          <t>FBA80075</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0GY86ZT1X</t>
+          <t>B0GXPGBQB1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6492,7 +6422,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6500,12 +6430,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA80104</t>
+          <t>FBA80076</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0GXY7YJWP</t>
+          <t>B0GY857139</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6515,7 +6445,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6523,10 +6453,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA80105</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>FBA80077</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>B0GY86ZT1X</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -6534,7 +6468,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -6542,10 +6476,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA80106</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>FBA80104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>B0GXY7YJWP</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -6553,7 +6491,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>UB-06 (AM-S2+AA-22)</t>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -6561,7 +6499,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6572,7 +6510,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6580,7 +6518,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA80110</t>
+          <t>FBA80106</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6591,7 +6529,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>UB-06 (AM-S2+AA-22)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6599,7 +6537,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA80114</t>
+          <t>FBA80109</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6610,7 +6548,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AH-53</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6618,7 +6556,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA80115</t>
+          <t>FBA80110</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6629,7 +6567,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>AH-50-DH</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6637,7 +6575,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA80116</t>
+          <t>FBA80114</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6648,7 +6586,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AH-40 Pro</t>
+          <t>AH-53</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6656,7 +6594,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA80117</t>
+          <t>FBA80115</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6667,7 +6605,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AH-53 Pro</t>
+          <t>AH-50-DH</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6675,7 +6613,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA80119</t>
+          <t>FBA80116</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6686,7 +6624,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>AM-C53</t>
+          <t>AH-40 Pro</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6694,7 +6632,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA80120</t>
+          <t>FBA80117</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6705,7 +6643,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AM-C54</t>
+          <t>AH-53 Pro</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6713,7 +6651,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA80121</t>
+          <t>FBA80119</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6724,7 +6662,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AM-C55</t>
+          <t>AM-C53</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6732,7 +6670,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA80122</t>
+          <t>FBA80120</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6743,7 +6681,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AM-C56</t>
+          <t>AM-C54</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6751,7 +6689,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA80123</t>
+          <t>FBA80121</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6762,7 +6700,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AM-W25</t>
+          <t>AM-C55</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6770,7 +6708,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA80124</t>
+          <t>FBA80122</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6781,7 +6719,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AA-26 Pro</t>
+          <t>AM-C56</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6789,7 +6727,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA80125</t>
+          <t>FBA80123</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6800,7 +6738,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>AA-28</t>
+          <t>AM-W25</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6808,7 +6746,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA80126</t>
+          <t>FBA80124</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6819,7 +6757,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AA-29</t>
+          <t>AA-26 Pro</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -6827,14 +6765,10 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA80128</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>B0H1H3K6B2</t>
-        </is>
-      </c>
+          <t>FBA80125</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -6842,7 +6776,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AA-28</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -6850,7 +6784,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA80129</t>
+          <t>FBA80126</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6861,7 +6795,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>HP4</t>
+          <t>AA-29</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6869,10 +6803,14 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA80130</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>FBA80128</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>B0H1H3K6B2</t>
+        </is>
+      </c>
       <c r="C169" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -6880,7 +6818,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>HPA1400</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6888,7 +6826,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA80131</t>
+          <t>FBA80129</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6899,7 +6837,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>HP4</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6907,7 +6845,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA80132</t>
+          <t>FBA80130</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6918,7 +6856,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PRE103</t>
+          <t>HPA1400</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6926,7 +6864,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA80133</t>
+          <t>FBA80131</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6937,7 +6875,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DI20</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -6945,7 +6883,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA80134</t>
+          <t>FBA80132</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6956,7 +6894,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>PRE103</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -6964,7 +6902,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA80135</t>
+          <t>FBA80133</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6975,7 +6913,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>IS-2</t>
+          <t>DI20</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -6983,7 +6921,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA80136</t>
+          <t>FBA80134</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -6994,7 +6932,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>IS-3</t>
+          <t>AC1</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7002,7 +6940,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA80137</t>
+          <t>FBA80135</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7013,7 +6951,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>IS-2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7021,7 +6959,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA80138</t>
+          <t>FBA80136</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -7032,7 +6970,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>MS155</t>
+          <t>IS-3</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -7040,14 +6978,10 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA80141</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>B0FJS57732</t>
-        </is>
-      </c>
+          <t>FBA80137</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>Audio Array</t>
@@ -7055,7 +6989,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7063,7 +6997,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA80142</t>
+          <t>FBA80138</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -7074,7 +7008,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>AM-C5 White</t>
+          <t>MS155</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7082,12 +7016,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA80143</t>
+          <t>FBA80141</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0H1MTP2ZP</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7097,7 +7031,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7105,22 +7039,18 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBAA75444</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>B0B65XBXKY</t>
-        </is>
-      </c>
+          <t>FBA80142</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>WM6023-8709-SIOC</t>
+          <t>AM-C5 White</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7128,22 +7058,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBAA75445</t>
+          <t>FBA80143</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0B68B17RT</t>
+          <t>B0H1MTP2ZP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>WM6822-167-SIOC</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7151,12 +7081,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBAA75446</t>
+          <t>FBAA75444</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0B689CVJW</t>
+          <t>B0B65XBXKY</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7166,7 +7096,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>WM6320-150-SIOC</t>
+          <t>WM6023-8709-SIOC</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7174,12 +7104,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBAA75447</t>
+          <t>FBAA75445</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0B688NL1N</t>
+          <t>B0B68B17RT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7189,7 +7119,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>WM6021-3081-BB</t>
+          <t>WM6822-167-SIOC</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7197,12 +7127,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBAA75448</t>
+          <t>FBAA75446</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0B68BJCL5</t>
+          <t>B0B689CVJW</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7212,7 +7142,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>WM6779-4892</t>
+          <t>WM6320-150-SIOC</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7220,12 +7150,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBAA75449</t>
+          <t>FBAA75447</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0B68DWHMR</t>
+          <t>B0B688NL1N</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7235,7 +7165,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>WM6779-4414-SIOC</t>
+          <t>WM6021-3081-BB</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7243,12 +7173,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBAA75450</t>
+          <t>FBAA75448</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0B68FKVC1</t>
+          <t>B0B68BJCL5</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7258,7 +7188,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>WM6822-150-SIOC</t>
+          <t>WM6779-4892</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7266,12 +7196,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBAA75451</t>
+          <t>FBAA75449</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0B68HQVXW</t>
+          <t>B0B68DWHMR</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7281,7 +7211,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>WM6023-7664-SIOC</t>
+          <t>WM6779-4414-SIOC</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7289,12 +7219,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBAA75452</t>
+          <t>FBAA75450</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0B68DCXS5</t>
+          <t>B0B68FKVC1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7304,7 +7234,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>WM6054-2364</t>
+          <t>WM6822-150-SIOC</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7312,12 +7242,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBAA75453</t>
+          <t>FBAA75451</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0B68GMXR9</t>
+          <t>B0B68HQVXW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7327,7 +7257,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>WM6705-3945</t>
+          <t>WM6023-7664-SIOC</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -7335,12 +7265,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBAA75454</t>
+          <t>FBAA75452</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0B6ZP6XK7</t>
+          <t>B0B68DCXS5</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7350,7 +7280,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>WM6070-3436</t>
+          <t>WM6054-2364</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7358,22 +7288,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBAM75673</t>
+          <t>FBAA75453</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0DFTVZPM8</t>
+          <t>B0B68GMXR9</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>WM6705-3945</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7381,22 +7311,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBAM79351</t>
+          <t>FBAA75454</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0D9KB2RTT</t>
+          <t>B0B6ZP6XK7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LE-01</t>
+          <t>WM6070-3436</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7404,22 +7334,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBAM79685</t>
+          <t>FBAM75673</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0DV8V3Y88</t>
+          <t>B0DFTVZPM8</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LE-08</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7427,22 +7357,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBI76419</t>
+          <t>FBAM79351</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B07MH7L6G8</t>
+          <t>B0D9KB2RTT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>WM-OD-CL</t>
+          <t>LE-01</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7450,22 +7380,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBK78924</t>
+          <t>FBAM79685</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0BGL16PJR</t>
+          <t>B0DV8V3Y88</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>K9</t>
+          <t>LE-08</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7473,22 +7403,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBK78979</t>
+          <t>FBI76419</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0CDPQXPC1</t>
+          <t>B07MH7L6G8</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>GS-01</t>
+          <t>WM-OD-CL</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7496,22 +7426,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBK78924</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0BGL16PJR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>K9</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -7519,12 +7449,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FBK79591</t>
+          <t>FBK78979</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0CDPQXPC1</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7534,7 +7464,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>KM-01</t>
+          <t>GS-01</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -7542,22 +7472,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FBK79792</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>B0FN4JG97R</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>HDMSP1ML</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -7565,12 +7495,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FBK80015</t>
+          <t>FBK79591</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7580,103 +7510,103 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>SPM-01</t>
-        </is>
-      </c>
-      <c r="E201" t="n">
-        <v>3899</v>
-      </c>
+          <t>KM-01</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FBK80024</t>
+          <t>FBK79792</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0FN4JG97R</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Nexlev</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>SS-02</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
-        <v>1699</v>
-      </c>
+          <t>HDMSP1ML</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FBM79783</t>
+          <t>FBK80015</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>AM-C47</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>SPM-01</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>3899</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FBO67237</t>
+          <t>FBK80024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>B079D8QRRL</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Nexlev</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>FS5447</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>SS-02</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>1699</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FBO76805</t>
+          <t>FBM79783</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>B0BG17DJQS</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>MK7303</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -7684,12 +7614,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FBO77014</t>
+          <t>FBO67237</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>B00CJ06DYG</t>
+          <t>B079D8QRRL</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7699,7 +7629,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AX1350</t>
+          <t>FS5447</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -7707,25 +7637,71 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>FBO76805</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>B0BG17DJQS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>MK7303</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FBO77014</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>B00CJ06DYG</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>AX1350</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
           <t>FBS79516</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>B0D85F9QCK</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Fossil</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>AX4614</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/week_landing_audit.xlsx
+++ b/data/processed/week_landing_audit.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7683,25 +7683,48 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>FBP79569</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>B0G1YKMFWT</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LE-06</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>FBS79516</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>B0D85F9QCK</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Fossil</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>AX4614</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7755,7 +7778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8858,7 +8881,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0GYS6CJD9</t>
+          <t>B0GYSMR9G2</t>
         </is>
       </c>
     </row>
@@ -8870,7 +8893,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0GYSMR9G2</t>
+          <t>B0GYSS16FJ</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8905,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0GYSS16FJ</t>
+          <t>B0GZKXXBC3</t>
         </is>
       </c>
     </row>
@@ -8894,29 +8917,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0GZKXXBC3</t>
+          <t>B0H25S24K1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>inbound_snapshot</t>
+          <t>margin_snapshot</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
-        <is>
-          <t>B0H25S24K1</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>margin_snapshot</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
         <is>
           <t>B0FN4GJ9S1</t>
         </is>
